--- a/public/templates/examples/A-009-RiskRegister-EXAMPLE-S.xlsx
+++ b/public/templates/examples/A-009-RiskRegister-EXAMPLE-S.xlsx
@@ -303,17 +303,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="Aptos"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="Aptos"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="Aptos"/>
       <family val="0"/>
     </font>
     <font>

--- a/public/templates/examples/A-009-RiskRegister-EXAMPLE-S.xlsx
+++ b/public/templates/examples/A-009-RiskRegister-EXAMPLE-S.xlsx
@@ -297,7 +297,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -544,19 +544,14 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>552240</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>552240</xdr:rowOff>
-    </xdr:to>
+    <xdr:ext cx="857250" cy="857250"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -581,7 +576,7 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
+  </xdr:oneCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -704,12 +699,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Aptos" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Aptos" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>

--- a/public/templates/examples/A-009-RiskRegister-EXAMPLE-S.xlsx
+++ b/public/templates/examples/A-009-RiskRegister-EXAMPLE-S.xlsx
@@ -5,12 +5,12 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0"/>
   </bookViews>
   <sheets>
     <sheet name="Register" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -208,7 +208,7 @@
     <t xml:space="preserve">POA&amp;M-005</t>
   </si>
   <si>
-    <t xml:space="preserve">Summary</t>
+    <t>Summary (as of 2026-04-09)</t>
   </si>
   <si>
     <t xml:space="preserve">Total risks</t>
@@ -290,8 +290,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -417,7 +418,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -467,6 +468,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1043,8 +1052,8 @@
       <c r="I12" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="J12" s="7" t="s">
-        <v>32</v>
+      <c r="J12" s="13">
+        <v>46218</v>
       </c>
       <c r="K12" s="7" t="s">
         <v>33</v>
@@ -1078,8 +1087,8 @@
       <c r="I13" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="J13" s="7" t="s">
-        <v>42</v>
+      <c r="J13" s="13">
+        <v>46157</v>
       </c>
       <c r="K13" s="7" t="s">
         <v>43</v>
@@ -1113,8 +1122,8 @@
       <c r="I14" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="J14" s="7" t="s">
-        <v>32</v>
+      <c r="J14" s="13">
+        <v>46218</v>
       </c>
       <c r="K14" s="7" t="s">
         <v>48</v>
@@ -1148,8 +1157,8 @@
       <c r="I15" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="J15" s="7" t="s">
-        <v>32</v>
+      <c r="J15" s="13">
+        <v>46218</v>
       </c>
       <c r="K15" s="7" t="s">
         <v>56</v>
@@ -1183,8 +1192,8 @@
       <c r="I16" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="J16" s="7" t="s">
-        <v>42</v>
+      <c r="J16" s="13">
+        <v>46120</v>
       </c>
       <c r="K16" s="7" t="s">
         <v>61</v>
@@ -1211,7 +1220,6 @@
       </c>
       <c r="C19" s="8" t="n">
         <f aca="false">COUNTA(A12:A16)</f>
-        <v>5</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1220,7 +1228,6 @@
       </c>
       <c r="C20" s="8" t="n">
         <f aca="false">COUNTIF(I12:I16,"Open")</f>
-        <v>2</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1229,7 +1236,6 @@
       </c>
       <c r="C21" s="8" t="n">
         <f aca="false">COUNTIF(I12:I16,"Treating")</f>
-        <v>2</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1238,7 +1244,6 @@
       </c>
       <c r="C22" s="8" t="n">
         <f aca="false">COUNTIF(I12:I16,"Accepted")</f>
-        <v>1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1247,7 +1252,6 @@
       </c>
       <c r="C23" s="8" t="n">
         <f aca="false">COUNTIF(I12:I16,"Closed")</f>
-        <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1255,8 +1259,7 @@
         <v>65</v>
       </c>
       <c r="C24" s="8" t="n">
-        <f aca="true">COUNTIF(J12:J16,"&lt;"&amp;TODAY())</f>
-        <v>0</v>
+        <f aca="true">COUNTIF(J12:J16,"&lt;"&amp;DATE(2026,4,9))</f>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1418,8 +1421,8 @@
       <c r="C39" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="D39" s="12" t="s">
-        <v>80</v>
+      <c r="D39" s="14">
+        <v>46070</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1432,8 +1435,8 @@
       <c r="C40" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="D40" s="12" t="s">
-        <v>80</v>
+      <c r="D40" s="14">
+        <v>46070</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1469,8 +1472,8 @@
       <c r="A44" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="B44" s="12" t="s">
-        <v>80</v>
+      <c r="B44" s="14">
+        <v>46070</v>
       </c>
       <c r="C44" s="12" t="s">
         <v>5</v>
@@ -1508,7 +1511,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
